--- a/MiniTemplate/Datas/subway.xlsx
+++ b/MiniTemplate/Datas/subway.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF1DB21-4BF3-4FB2-BE5B-88A25180114C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CED44A1-10E2-4289-BD05-3E6AA1CBE1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,9 +100,6 @@
     <t>社区</t>
   </si>
   <si>
-    <t>默认解锁的起始地点</t>
-  </si>
-  <si>
     <t>Assets/Art/Community/SpritesBig/community_station.png[community_station]</t>
   </si>
   <si>
@@ -113,6 +110,10 @@
   </si>
   <si>
     <t>Assets/Art/Community/SpritesBig/subway_fish.png[subway_fish]</t>
+  </si>
+  <si>
+    <t>温馨的社区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -621,10 +622,10 @@
         <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -646,13 +647,13 @@
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="F6" s="1">
         <v>200</v>

--- a/MiniTemplate/Datas/subway.xlsx
+++ b/MiniTemplate/Datas/subway.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CED44A1-10E2-4289-BD05-3E6AA1CBE1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430F8E52-FE1B-4FAD-90FD-BC7585D28D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -113,6 +113,18 @@
   </si>
   <si>
     <t>温馨的社区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>港口</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>商贸交易的地方，可以淘到好东西</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Community/SpritesBig/Subway_harbor.png[Subway_harbor]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -472,20 +484,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="49.6640625" customWidth="1"/>
-    <col min="5" max="5" width="61.44140625" customWidth="1"/>
-    <col min="6" max="6" width="23.21875" customWidth="1"/>
-    <col min="7" max="7" width="57.77734375" customWidth="1"/>
-    <col min="8" max="8" width="31.33203125" customWidth="1"/>
-    <col min="9" max="9" width="32.21875" customWidth="1"/>
+    <col min="4" max="4" width="49.625" customWidth="1"/>
+    <col min="5" max="5" width="68.375" customWidth="1"/>
+    <col min="6" max="6" width="23.25" customWidth="1"/>
+    <col min="7" max="7" width="57.75" customWidth="1"/>
+    <col min="8" max="8" width="31.375" customWidth="1"/>
+    <col min="9" max="9" width="32.25" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -517,7 +529,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -549,7 +561,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -581,7 +593,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -613,7 +625,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
       <c r="B5" s="1">
         <v>1</v>
@@ -641,7 +653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
       <c r="B6" s="1">
         <v>2</v>
@@ -656,7 +668,7 @@
         <v>29</v>
       </c>
       <c r="F6" s="1">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6">
@@ -666,6 +678,32 @@
         <v>0</v>
       </c>
       <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>0</v>
       </c>
     </row>
